--- a/OperationDataStorage/2024-03-18.xlsx
+++ b/OperationDataStorage/2024-03-18.xlsx
@@ -299,6 +299,45 @@
   </x:si>
   <x:si>
     <x:t>1990-01-01:03:59:42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:00:50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:01:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:01:04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:01:07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:01:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:22:21</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4036,6 +4075,664 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
+    <x:row r="73" spans="1:15">
+      <x:c r="A73" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F73" s="0">
+        <x:v>2350</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H73" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J73" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K73" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L73" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M73" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N73" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O73" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:15">
+      <x:c r="A74" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F74" s="0">
+        <x:v>2349</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H74" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J74" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K74" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L74" s="0">
+        <x:v>0.0299999993294477</x:v>
+      </x:c>
+      <x:c r="M74" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N74" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O74" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:15">
+      <x:c r="A75" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F75" s="0">
+        <x:v>2351</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H75" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J75" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K75" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L75" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M75" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N75" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O75" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:15">
+      <x:c r="A76" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F76" s="0">
+        <x:v>2352</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H76" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J76" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K76" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L76" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M76" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N76" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O76" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:15">
+      <x:c r="A77" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F77" s="0">
+        <x:v>2353</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H77" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J77" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K77" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L77" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M77" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N77" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O77" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:15">
+      <x:c r="A78" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F78" s="0">
+        <x:v>2354</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H78" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I78" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J78" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K78" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L78" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M78" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N78" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O78" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:15">
+      <x:c r="A79" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F79" s="0">
+        <x:v>2355</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H79" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J79" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K79" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L79" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M79" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N79" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O79" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:15">
+      <x:c r="A80" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F80" s="0">
+        <x:v>2356</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H80" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J80" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K80" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L80" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M80" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N80" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O80" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:15">
+      <x:c r="A81" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F81" s="0">
+        <x:v>2357</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H81" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J81" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K81" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L81" s="0">
+        <x:v>0.129999995231628</x:v>
+      </x:c>
+      <x:c r="M81" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N81" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O81" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:15">
+      <x:c r="A82" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F82" s="0">
+        <x:v>2358</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H82" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J82" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K82" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L82" s="0">
+        <x:v>0.150000005960464</x:v>
+      </x:c>
+      <x:c r="M82" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N82" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O82" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:15">
+      <x:c r="A83" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F83" s="0">
+        <x:v>2359</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H83" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J83" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K83" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L83" s="0">
+        <x:v>0.129999995231628</x:v>
+      </x:c>
+      <x:c r="M83" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N83" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O83" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:15">
+      <x:c r="A84" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F84" s="0">
+        <x:v>2360</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H84" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J84" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K84" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L84" s="0">
+        <x:v>0.129999995231628</x:v>
+      </x:c>
+      <x:c r="M84" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N84" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O84" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:15">
+      <x:c r="A85" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F85" s="0">
+        <x:v>2361</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H85" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J85" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K85" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L85" s="0">
+        <x:v>0.140000000596046</x:v>
+      </x:c>
+      <x:c r="M85" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N85" s="0">
+        <x:v>1999</x:v>
+      </x:c>
+      <x:c r="O85" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:15">
+      <x:c r="A86" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F86" s="0">
+        <x:v>2362</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H86" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J86" s="0">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="K86" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L86" s="0">
+        <x:v>0.109999999403954</x:v>
+      </x:c>
+      <x:c r="M86" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="N86" s="0">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="O86" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
